--- a/app/exceltemplates/見積書原本.xlsx
+++ b/app/exceltemplates/見積書原本.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2741BD-F3A4-4C07-8C3E-A3E3AC9C61B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B573C8-EB41-40B7-BE2A-096875E11EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -597,7 +597,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -668,6 +668,8 @@
     <xf numFmtId="38" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
@@ -1469,6 +1471,7 @@
       <c r="A31" t="s">
         <v>14</v>
       </c>
+      <c r="B31" s="35"/>
       <c r="E31" s="32"/>
       <c r="F31" s="22"/>
       <c r="G31" s="33"/>
@@ -1477,16 +1480,19 @@
       <c r="A33" t="s">
         <v>11</v>
       </c>
+      <c r="B33" s="35"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>13</v>
       </c>
+      <c r="B35" s="35"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>2</v>
       </c>
+      <c r="B37" s="35"/>
     </row>
     <row r="39" spans="1:7" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="40" spans="1:7" x14ac:dyDescent="0.15">
@@ -1501,43 +1507,43 @@
       <c r="G40" s="5"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A41" s="6"/>
+      <c r="A41" s="34"/>
       <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A42" s="6"/>
+      <c r="A42" s="34"/>
       <c r="G42" s="7"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A43" s="6"/>
+      <c r="A43" s="34"/>
       <c r="G43" s="7"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A44" s="6"/>
+      <c r="A44" s="34"/>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A45" s="6"/>
+      <c r="A45" s="34"/>
       <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A46" s="6"/>
+      <c r="A46" s="34"/>
       <c r="G46" s="7"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A47" s="6"/>
+      <c r="A47" s="34"/>
       <c r="G47" s="7"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A48" s="6"/>
+      <c r="A48" s="34"/>
       <c r="G48" s="7"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A49" s="6"/>
+      <c r="A49" s="34"/>
       <c r="G49" s="7"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A50" s="6"/>
+      <c r="A50" s="34"/>
       <c r="G50" s="7"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">
@@ -1571,6 +1577,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="32.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="35"/>
       <c r="C1" s="19" t="s">
         <v>19</v>
       </c>
@@ -1888,6 +1895,7 @@
       <c r="A32" t="s">
         <v>14</v>
       </c>
+      <c r="B32" s="35"/>
       <c r="E32" s="32"/>
       <c r="F32" s="22"/>
       <c r="G32" s="21"/>
@@ -1896,16 +1904,19 @@
       <c r="A34" t="s">
         <v>11</v>
       </c>
+      <c r="B34" s="35"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>13</v>
       </c>
+      <c r="B36" s="35"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>2</v>
       </c>
+      <c r="B38" s="35"/>
     </row>
     <row r="39" spans="1:7" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="40" spans="1:7" x14ac:dyDescent="0.15">
@@ -1920,43 +1931,43 @@
       <c r="G40" s="5"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A41" s="6"/>
+      <c r="A41" s="34"/>
       <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A42" s="6"/>
+      <c r="A42" s="34"/>
       <c r="G42" s="7"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A43" s="6"/>
+      <c r="A43" s="34"/>
       <c r="G43" s="7"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A44" s="6"/>
+      <c r="A44" s="34"/>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A45" s="6"/>
+      <c r="A45" s="34"/>
       <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A46" s="6"/>
+      <c r="A46" s="34"/>
       <c r="G46" s="7"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A47" s="6"/>
+      <c r="A47" s="34"/>
       <c r="G47" s="7"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A48" s="6"/>
+      <c r="A48" s="34"/>
       <c r="G48" s="7"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A49" s="6"/>
+      <c r="A49" s="34"/>
       <c r="G49" s="7"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A50" s="6"/>
+      <c r="A50" s="34"/>
       <c r="G50" s="7"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">

--- a/app/exceltemplates/見積書原本.xlsx
+++ b/app/exceltemplates/見積書原本.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B573C8-EB41-40B7-BE2A-096875E11EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D8DB4F-5A82-4363-8EC6-29A979B02CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
